--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117949394</v>
+        <v>117949524</v>
       </c>
       <c r="B2" t="n">
-        <v>5261</v>
+        <v>57440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100155</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre timmerman</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Acanthocinus griseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,20 +713,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>frispringande/krypande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -771,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -781,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -808,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117949524</v>
+        <v>117949394</v>
       </c>
       <c r="B3" t="n">
-        <v>57440</v>
+        <v>5261</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100155</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre timmerman</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Acanthocinus griseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,11 +837,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>frispringande/krypande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117949524</v>
       </c>
       <c r="B2" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -811,11 +811,11 @@
         <v>117949524</v>
       </c>
       <c r="B3" t="n">
-        <v>57443</v>
+        <v>57518</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117949524</v>
       </c>
       <c r="B3" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117949524</v>
       </c>
       <c r="B3" t="n">
-        <v>57522</v>
+        <v>57525</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117949524</v>
       </c>
       <c r="B3" t="n">
-        <v>57525</v>
+        <v>57527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117949524</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -826,11 +826,6 @@
       <c r="E3" t="n">
         <v>103021</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 7747-2023 artfynd.xlsx
+++ b/artfynd/A 7747-2023 artfynd.xlsx
@@ -811,7 +811,7 @@
         <v>117949524</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,6 +825,11 @@
       </c>
       <c r="E3" t="n">
         <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
